--- a/docs/transactions.xlsx
+++ b/docs/transactions.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkData\SusuRepos\final-qualifying-work\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D81AF3D-331C-46F5-A08E-7267022B1896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
   <si>
     <t>Берем репозитории созданные с 2021 по 2022</t>
   </si>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -149,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -160,23 +161,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -191,7 +181,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -490,153 +480,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51" style="7" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="9" max="9" width="26.21875" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" customWidth="1"/>
+    <col min="11" max="11" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.33203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="K2" s="4"/>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="D3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="I3" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+      <c r="J3" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="K3" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+      <c r="L3" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
         <v>9</v>
       </c>
     </row>
